--- a/database/catalogue.xlsx
+++ b/database/catalogue.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="988" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="989" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="269">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">Japan</t>
   </si>
   <si>
-    <t xml:space="preserve">Basaltic-andesite</t>
+    <t xml:space="preserve">Basalt-andesite</t>
   </si>
   <si>
     <t xml:space="preserve">1981-1989</t>
@@ -1059,7 +1059,7 @@
     <t xml:space="preserve">Shield volcano</t>
   </si>
   <si>
-    <t xml:space="preserve">Basalt shield &amp; Basalt–rhyolite caldera</t>
+    <t xml:space="preserve">Basalt shield, Basalt–rhyolite caldera</t>
   </si>
   <si>
     <r>
@@ -1518,9 +1518,6 @@
     <t xml:space="preserve">Complex volcano</t>
   </si>
   <si>
-    <t xml:space="preserve">Basaltic</t>
-  </si>
-  <si>
     <t xml:space="preserve">LRET</t>
   </si>
   <si>
@@ -2046,9 +2043,6 @@
     <t xml:space="preserve">Somma volcano</t>
   </si>
   <si>
-    <t xml:space="preserve">Basal–dacite</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -2373,9 +2367,6 @@
   </si>
   <si>
     <t xml:space="preserve">Equador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andesitic</t>
   </si>
   <si>
     <r>
@@ -2444,7 +2435,7 @@
     <numFmt numFmtId="168" formatCode="#,##0"/>
     <numFmt numFmtId="169" formatCode="0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -2474,13 +2465,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2582,7 +2566,7 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2590,19 +2574,35 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2610,31 +2610,15 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2722,36 +2706,36 @@
   <dimension ref="A1:AE65536"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col collapsed="false" hidden="false" max="1" min="1" style="1" width="13.6893617021277"/>
-    <col collapsed="false" hidden="false" max="2" min="2" style="1" width="14.3234042553192"/>
-    <col collapsed="false" hidden="false" max="3" min="3" style="1" width="9.36595744680851"/>
-    <col collapsed="false" hidden="false" max="4" min="4" style="1" width="8.91914893617021"/>
-    <col collapsed="false" hidden="false" max="5" min="5" style="1" width="14.3234042553192"/>
-    <col collapsed="false" hidden="false" max="6" min="6" style="1" width="14.4127659574468"/>
-    <col collapsed="false" hidden="false" max="7" min="7" style="1" width="8.55744680851064"/>
-    <col collapsed="false" hidden="false" max="8" min="8" style="1" width="8.37872340425532"/>
-    <col collapsed="false" hidden="false" max="9" min="9" style="1" width="11.5276595744681"/>
-    <col collapsed="false" hidden="false" max="10" min="10" style="1" width="15.0425531914894"/>
-    <col collapsed="false" hidden="false" max="11" min="11" style="1" width="11.0808510638298"/>
-    <col collapsed="false" hidden="false" max="12" min="12" style="1" width="5.04255319148936"/>
-    <col collapsed="false" hidden="false" max="13" min="13" style="1" width="8.1063829787234"/>
-    <col collapsed="false" hidden="false" max="14" min="14" style="1" width="6.21702127659574"/>
-    <col collapsed="false" hidden="false" max="15" min="15" style="1" width="7.47659574468085"/>
-    <col collapsed="false" hidden="false" max="16" min="16" style="1" width="9.36595744680851"/>
-    <col collapsed="false" hidden="false" max="17" min="17" style="1" width="46.0255319148936"/>
-    <col collapsed="false" hidden="false" max="18" min="18" style="1" width="13.2425531914894"/>
-    <col collapsed="false" hidden="false" max="19" min="19" style="1" width="9.18723404255319"/>
-    <col collapsed="false" hidden="false" max="20" min="20" style="1" width="9.36595744680851"/>
-    <col collapsed="false" hidden="false" max="22" min="21" style="1" width="9.54893617021277"/>
-    <col collapsed="false" hidden="false" max="23" min="23" style="1" width="9.36595744680851"/>
-    <col collapsed="false" hidden="false" max="24" min="24" style="1" width="8.37872340425532"/>
-    <col collapsed="false" hidden="false" max="25" min="25" style="1" width="12.2510638297872"/>
-    <col collapsed="false" hidden="false" max="26" min="26" style="1" width="9.18723404255319"/>
-    <col collapsed="false" hidden="false" max="27" min="27" style="1" width="9.00851063829787"/>
-    <col collapsed="false" hidden="false" max="28" min="28" style="1" width="12.9702127659574"/>
-    <col collapsed="false" hidden="false" max="29" min="29" style="1" width="22.6085106382979"/>
-    <col collapsed="false" hidden="false" max="31" min="30" style="1" width="11.5276595744681"/>
-    <col collapsed="false" hidden="false" max="1025" min="32" style="1" width="11.8893617021277"/>
+    <col collapsed="false" hidden="false" max="1" min="1" style="1" width="14.2297872340426"/>
+    <col collapsed="false" hidden="false" max="2" min="2" style="1" width="14.863829787234"/>
+    <col collapsed="false" hidden="false" max="3" min="3" style="1" width="9.63829787234043"/>
+    <col collapsed="false" hidden="false" max="4" min="4" style="1" width="9.18723404255319"/>
+    <col collapsed="false" hidden="false" max="5" min="5" style="1" width="14.863829787234"/>
+    <col collapsed="false" hidden="false" max="6" min="6" style="1" width="14.9531914893617"/>
+    <col collapsed="false" hidden="false" max="7" min="7" style="1" width="8.82553191489362"/>
+    <col collapsed="false" hidden="false" max="8" min="8" style="1" width="8.6468085106383"/>
+    <col collapsed="false" hidden="false" max="9" min="9" style="1" width="11.8893617021277"/>
+    <col collapsed="false" hidden="false" max="10" min="10" style="1" width="15.4936170212766"/>
+    <col collapsed="false" hidden="false" max="11" min="11" style="1" width="11.4382978723404"/>
+    <col collapsed="false" hidden="false" max="12" min="12" style="1" width="5.13617021276596"/>
+    <col collapsed="false" hidden="false" max="13" min="13" style="1" width="8.37872340425532"/>
+    <col collapsed="false" hidden="false" max="14" min="14" style="1" width="6.39574468085106"/>
+    <col collapsed="false" hidden="false" max="15" min="15" style="1" width="7.65531914893617"/>
+    <col collapsed="false" hidden="false" max="16" min="16" style="1" width="9.63829787234043"/>
+    <col collapsed="false" hidden="false" max="17" min="17" style="1" width="47.6468085106383"/>
+    <col collapsed="false" hidden="false" max="18" min="18" style="1" width="13.6893617021277"/>
+    <col collapsed="false" hidden="false" max="19" min="19" style="1" width="9.45957446808511"/>
+    <col collapsed="false" hidden="false" max="20" min="20" style="1" width="9.63829787234043"/>
+    <col collapsed="false" hidden="false" max="22" min="21" style="1" width="9.81702127659574"/>
+    <col collapsed="false" hidden="false" max="23" min="23" style="1" width="9.63829787234043"/>
+    <col collapsed="false" hidden="false" max="24" min="24" style="1" width="8.6468085106383"/>
+    <col collapsed="false" hidden="false" max="25" min="25" style="1" width="12.7021276595745"/>
+    <col collapsed="false" hidden="false" max="26" min="26" style="1" width="9.45957446808511"/>
+    <col collapsed="false" hidden="false" max="27" min="27" style="1" width="9.27659574468085"/>
+    <col collapsed="false" hidden="false" max="28" min="28" style="1" width="13.4212765957447"/>
+    <col collapsed="false" hidden="false" max="29" min="29" style="1" width="23.4170212765957"/>
+    <col collapsed="false" hidden="false" max="31" min="30" style="1" width="11.8893617021277"/>
+    <col collapsed="false" hidden="false" max="1025" min="32" style="1" width="12.3404255319149"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3303,7 +3287,7 @@
       </c>
       <c r="I7" s="6" t="str">
         <f aca="false">I6</f>
-        <v>Basaltic-andesite</v>
+        <v>Basalt-andesite</v>
       </c>
       <c r="J7" s="6" t="n">
         <f aca="false">J6</f>
@@ -3391,7 +3375,7 @@
       </c>
       <c r="I8" s="6" t="str">
         <f aca="false">I7</f>
-        <v>Basaltic-andesite</v>
+        <v>Basalt-andesite</v>
       </c>
       <c r="J8" s="6" t="n">
         <f aca="false">J7</f>
@@ -4959,7 +4943,7 @@
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
       <c r="I33" s="12" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="J33" s="6"/>
       <c r="K33" s="6"/>
@@ -4968,10 +4952,10 @@
       <c r="N33" s="6"/>
       <c r="O33" s="6"/>
       <c r="P33" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q33" s="12" t="s">
         <v>212</v>
-      </c>
-      <c r="Q33" s="12" t="s">
-        <v>213</v>
       </c>
       <c r="R33" s="13"/>
       <c r="S33" s="13"/>
@@ -4984,14 +4968,14 @@
       <c r="Z33" s="6"/>
       <c r="AA33" s="6"/>
       <c r="AC33" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AD33" s="6"/>
       <c r="AE33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>70</v>
@@ -5006,7 +4990,7 @@
         <v>33</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G34" s="6"/>
       <c r="H34" s="6"/>
@@ -5023,7 +5007,7 @@
         <v>134</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="R34" s="13"/>
       <c r="S34" s="13"/>
@@ -5036,14 +5020,14 @@
       <c r="Z34" s="6"/>
       <c r="AA34" s="6"/>
       <c r="AC34" s="15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AD34" s="6"/>
       <c r="AE34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>70</v>
@@ -5072,10 +5056,10 @@
       <c r="N35" s="6"/>
       <c r="O35" s="6"/>
       <c r="P35" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R35" s="13"/>
       <c r="S35" s="13"/>
@@ -5088,14 +5072,14 @@
       <c r="Z35" s="6"/>
       <c r="AA35" s="6"/>
       <c r="AC35" s="15" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AD35" s="6"/>
       <c r="AE35" s="6"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>70</v>
@@ -5129,7 +5113,7 @@
         <v>134</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R36" s="13"/>
       <c r="S36" s="12"/>
@@ -5142,14 +5126,14 @@
       <c r="Z36" s="6"/>
       <c r="AA36" s="6"/>
       <c r="AC36" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AD36" s="6"/>
       <c r="AE36" s="6"/>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>70</v>
@@ -5178,10 +5162,10 @@
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="P37" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R37" s="13"/>
       <c r="S37" s="12"/>
@@ -5194,17 +5178,17 @@
       <c r="Z37" s="6"/>
       <c r="AA37" s="6"/>
       <c r="AC37" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AD37" s="6"/>
       <c r="AE37" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="C38" s="7" t="n">
         <v>56.056</v>
@@ -5230,10 +5214,10 @@
       <c r="N38" s="6"/>
       <c r="O38" s="6"/>
       <c r="P38" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R38" s="13"/>
       <c r="S38" s="12"/>
@@ -5246,17 +5230,17 @@
       <c r="Z38" s="6"/>
       <c r="AA38" s="6"/>
       <c r="AC38" s="12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AD38" s="6"/>
       <c r="AE38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>232</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>233</v>
       </c>
       <c r="C39" s="7" t="n">
         <v>19.421</v>
@@ -5266,7 +5250,7 @@
         <v>-155.287</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>173</v>
@@ -5286,7 +5270,7 @@
         <v>134</v>
       </c>
       <c r="Q39" s="12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R39" s="13"/>
       <c r="S39" s="12"/>
@@ -5299,17 +5283,17 @@
       <c r="Z39" s="6"/>
       <c r="AA39" s="6"/>
       <c r="AC39" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AD39" s="6"/>
       <c r="AE39" s="6"/>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C40" s="7" t="n">
         <f aca="false">C39</f>
@@ -5320,7 +5304,7 @@
         <v>-155.287</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>173</v>
@@ -5340,7 +5324,7 @@
         <v>134</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R40" s="13"/>
       <c r="S40" s="12"/>
@@ -5353,17 +5337,17 @@
       <c r="Z40" s="6"/>
       <c r="AA40" s="6"/>
       <c r="AC40" s="12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AD40" s="6"/>
       <c r="AE40" s="6"/>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>240</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>241</v>
       </c>
       <c r="C41" s="7" t="n">
         <v>40.821</v>
@@ -5375,12 +5359,12 @@
         <v>33</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
       <c r="I41" s="12" t="s">
-        <v>243</v>
+        <v>102</v>
       </c>
       <c r="J41" s="6"/>
       <c r="K41" s="6"/>
@@ -5392,7 +5376,7 @@
         <v>134</v>
       </c>
       <c r="Q41" s="12" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R41" s="13"/>
       <c r="S41" s="12"/>
@@ -5405,17 +5389,17 @@
       <c r="Z41" s="6"/>
       <c r="AA41" s="6"/>
       <c r="AC41" s="12" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AD41" s="6"/>
       <c r="AE41" s="6"/>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C42" s="7" t="n">
         <v>40.827</v>
@@ -5444,7 +5428,7 @@
         <v>134</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="R42" s="13"/>
       <c r="S42" s="12"/>
@@ -5457,17 +5441,17 @@
       <c r="Z42" s="6"/>
       <c r="AA42" s="6"/>
       <c r="AC42" s="15" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AD42" s="6"/>
       <c r="AE42" s="6"/>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C43" s="7" t="n">
         <v>37.748</v>
@@ -5496,7 +5480,7 @@
         <v>134</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="R43" s="13"/>
       <c r="S43" s="12"/>
@@ -5509,17 +5493,17 @@
       <c r="Z43" s="6"/>
       <c r="AA43" s="6"/>
       <c r="AC43" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="AD43" s="6"/>
       <c r="AE43" s="6"/>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C44" s="7" t="n">
         <v>38.789</v>
@@ -5558,10 +5542,10 @@
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C45" s="7" t="n">
         <v>15.13</v>
@@ -5590,7 +5574,7 @@
         <v>134</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R45" s="13"/>
       <c r="S45" s="12"/>
@@ -5603,17 +5587,17 @@
       <c r="Z45" s="6"/>
       <c r="AA45" s="6"/>
       <c r="AC45" s="15" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="AD45" s="6"/>
       <c r="AE45" s="6"/>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C46" s="7" t="n">
         <v>4.892</v>
@@ -5643,7 +5627,7 @@
         <v>134</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="R46" s="13"/>
       <c r="S46" s="12"/>
@@ -5656,17 +5640,17 @@
       <c r="Z46" s="6"/>
       <c r="AA46" s="6"/>
       <c r="AC46" s="15" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AD46" s="6"/>
       <c r="AE46" s="6"/>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C47" s="7" t="n">
         <f aca="false">-1.467</f>
@@ -5685,7 +5669,7 @@
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
       <c r="I47" s="12" t="s">
-        <v>263</v>
+        <v>35</v>
       </c>
       <c r="J47" s="6"/>
       <c r="K47" s="6"/>
@@ -5697,7 +5681,7 @@
         <v>134</v>
       </c>
       <c r="Q47" s="12" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="R47" s="13"/>
       <c r="S47" s="12"/>
@@ -5710,17 +5694,17 @@
       <c r="Z47" s="6"/>
       <c r="AA47" s="6"/>
       <c r="AC47" s="15" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="AD47" s="6"/>
       <c r="AE47" s="6"/>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C48" s="7" t="n">
         <v>28</v>
@@ -5729,15 +5713,15 @@
         <v>-15.58</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
       <c r="I48" s="12" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="J48" s="6"/>
       <c r="K48" s="6"/>
@@ -5749,7 +5733,7 @@
         <v>134</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="R48" s="13"/>
       <c r="S48" s="12"/>
@@ -5762,7 +5746,7 @@
       <c r="Z48" s="6"/>
       <c r="AA48" s="6"/>
       <c r="AC48" s="15" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AD48" s="6"/>
       <c r="AE48" s="6"/>
